--- a/doc/transition_matrix.xlsx
+++ b/doc/transition_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wim/Desktop/projects/structuralism_simulation/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C44FA445-6915-934D-8BB7-4A8502B181E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73297802-FB82-6449-A125-2BEFFA2705FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="460" windowWidth="25300" windowHeight="21220" xr2:uid="{C237673F-38BF-A049-98FF-B6FBA60D612A}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="41">
   <si>
     <t>H1</t>
   </si>
@@ -863,8 +863,8 @@
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
-        <v>1</v>
+      <c r="B3" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="C3" s="4">
         <v>1</v>
@@ -5721,8 +5721,8 @@
       <c r="AK41" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AL41" s="8">
-        <v>1</v>
+      <c r="AL41" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="AM41" s="2" t="s">
         <v>40</v>

--- a/doc/transition_matrix.xlsx
+++ b/doc/transition_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wim/Desktop/projects/structuralism_simulation/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73297802-FB82-6449-A125-2BEFFA2705FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8738C757-FBB9-4D4A-8314-B13F644DB50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="460" windowWidth="25300" windowHeight="21220" xr2:uid="{C237673F-38BF-A049-98FF-B6FBA60D612A}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="41">
   <si>
     <t>H1</t>
   </si>
@@ -1637,8 +1637,8 @@
       <c r="I9" s="4">
         <v>1</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>40</v>
+      <c r="J9" s="5">
+        <v>1</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>40</v>
@@ -1759,8 +1759,8 @@
       <c r="H10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>40</v>
+      <c r="I10" s="5">
+        <v>1</v>
       </c>
       <c r="J10" s="4">
         <v>1</v>
@@ -2533,8 +2533,8 @@
       <c r="P16" s="4">
         <v>1</v>
       </c>
-      <c r="Q16" s="3" t="s">
-        <v>40</v>
+      <c r="Q16" s="5">
+        <v>1</v>
       </c>
       <c r="R16" s="3" t="s">
         <v>40</v>

--- a/doc/transition_matrix.xlsx
+++ b/doc/transition_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wim/Desktop/projects/structuralism_simulation/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8738C757-FBB9-4D4A-8314-B13F644DB50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BF2F08-D36E-9542-9565-CF664FF09D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4760" yWindow="460" windowWidth="25300" windowHeight="21220" xr2:uid="{C237673F-38BF-A049-98FF-B6FBA60D612A}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="42">
   <si>
     <t>H1</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>H41</t>
   </si>
 </sst>
 </file>
@@ -603,15 +606,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC42CF5-B0EF-7C4D-BB1B-DFD722DD791F}">
-  <dimension ref="A1:AO41"/>
+  <dimension ref="A1:AP42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="7" customWidth="1"/>
-    <col min="2" max="41" width="4.83203125" style="1" customWidth="1"/>
-    <col min="42" max="16384" width="10.83203125" style="1"/>
+    <col min="2" max="42" width="4.83203125" style="1" customWidth="1"/>
+    <col min="43" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="7" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:42" s="7" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6"/>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -733,8 +736,11 @@
       <c r="AO1" s="6" t="s">
         <v>39</v>
       </c>
+      <c r="AP1" s="6" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -858,8 +864,11 @@
       <c r="AO2" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP2" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="3" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -983,8 +992,11 @@
       <c r="AO3" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP3" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
@@ -1108,8 +1120,11 @@
       <c r="AO4" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP4" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="5" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
@@ -1233,8 +1248,11 @@
       <c r="AO5" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP5" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="6" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1358,8 +1376,11 @@
       <c r="AO6" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP6" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="7" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
@@ -1483,8 +1504,11 @@
       <c r="AO7" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP7" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="8" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
@@ -1608,8 +1632,11 @@
       <c r="AO8" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP8" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="9" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
@@ -1733,8 +1760,11 @@
       <c r="AO9" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP9" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
@@ -1858,8 +1888,11 @@
       <c r="AO10" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP10" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
@@ -1983,8 +2016,11 @@
       <c r="AO11" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP11" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="12" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
@@ -2108,8 +2144,11 @@
       <c r="AO12" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP12" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>11</v>
       </c>
@@ -2233,8 +2272,11 @@
       <c r="AO13" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP13" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
@@ -2358,8 +2400,11 @@
       <c r="AO14" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP14" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>13</v>
       </c>
@@ -2483,8 +2528,11 @@
       <c r="AO15" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP15" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>14</v>
       </c>
@@ -2608,8 +2656,11 @@
       <c r="AO16" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP16" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="17" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>15</v>
       </c>
@@ -2733,8 +2784,11 @@
       <c r="AO17" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP17" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="18" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>16</v>
       </c>
@@ -2858,8 +2912,11 @@
       <c r="AO18" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP18" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="19" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>17</v>
       </c>
@@ -2983,8 +3040,11 @@
       <c r="AO19" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP19" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="20" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>18</v>
       </c>
@@ -3108,8 +3168,11 @@
       <c r="AO20" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP20" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="21" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>19</v>
       </c>
@@ -3233,8 +3296,11 @@
       <c r="AO21" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP21" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="22" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>20</v>
       </c>
@@ -3358,8 +3424,11 @@
       <c r="AO22" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP22" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="23" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>21</v>
       </c>
@@ -3483,8 +3552,11 @@
       <c r="AO23" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP23" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="24" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>22</v>
       </c>
@@ -3608,8 +3680,11 @@
       <c r="AO24" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP24" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="25" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>23</v>
       </c>
@@ -3733,8 +3808,11 @@
       <c r="AO25" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP25" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="26" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>24</v>
       </c>
@@ -3858,8 +3936,11 @@
       <c r="AO26" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP26" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="27" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>25</v>
       </c>
@@ -3983,8 +4064,11 @@
       <c r="AO27" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP27" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="28" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>26</v>
       </c>
@@ -4108,8 +4192,11 @@
       <c r="AO28" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP28" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="29" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>27</v>
       </c>
@@ -4233,8 +4320,11 @@
       <c r="AO29" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP29" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="30" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>28</v>
       </c>
@@ -4358,8 +4448,11 @@
       <c r="AO30" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP30" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="31" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>29</v>
       </c>
@@ -4483,8 +4576,11 @@
       <c r="AO31" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP31" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="32" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>30</v>
       </c>
@@ -4608,8 +4704,11 @@
       <c r="AO32" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP32" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="33" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>31</v>
       </c>
@@ -4733,8 +4832,11 @@
       <c r="AO33" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP33" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="34" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>32</v>
       </c>
@@ -4858,8 +4960,11 @@
       <c r="AO34" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP34" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="35" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
         <v>33</v>
       </c>
@@ -4983,8 +5088,11 @@
       <c r="AO35" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP35" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="36" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>34</v>
       </c>
@@ -5108,8 +5216,11 @@
       <c r="AO36" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP36" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="37" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>35</v>
       </c>
@@ -5233,8 +5344,11 @@
       <c r="AO37" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP37" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="38" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>36</v>
       </c>
@@ -5358,8 +5472,11 @@
       <c r="AO38" s="8">
         <v>1</v>
       </c>
+      <c r="AP38" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="39" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>37</v>
       </c>
@@ -5483,8 +5600,11 @@
       <c r="AO39" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP39" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="40" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
         <v>38</v>
       </c>
@@ -5608,8 +5728,11 @@
       <c r="AO40" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="AP40" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="41" spans="1:41" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
         <v>39</v>
       </c>
@@ -5721,8 +5844,8 @@
       <c r="AK41" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AL41" s="2" t="s">
-        <v>40</v>
+      <c r="AL41" s="8">
+        <v>1</v>
       </c>
       <c r="AM41" s="2" t="s">
         <v>40</v>
@@ -5731,6 +5854,137 @@
         <v>40</v>
       </c>
       <c r="AO41" s="4">
+        <v>1</v>
+      </c>
+      <c r="AP41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:42" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="T42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AI42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AJ42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AK42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AL42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP42" s="4">
         <v>1</v>
       </c>
     </row>
